--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ.xlsx
@@ -286,7 +286,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -1485,7 +1485,7 @@
         <v>6</v>
       </c>
       <c r="D22" s="7">
-        <v>1.9637</v>
+        <v>1.963716</v>
       </c>
       <c r="E22" s="6">
         <v>553.12</v>
@@ -1505,7 +1505,7 @@
         <v>7</v>
       </c>
       <c r="D23" s="7">
-        <v>1.5154</v>
+        <v>1.515432</v>
       </c>
       <c r="E23" s="6">
         <v>291.66</v>
@@ -1545,7 +1545,7 @@
         <v>2</v>
       </c>
       <c r="D25" s="7">
-        <v>1.8046</v>
+        <v>1.804565</v>
       </c>
       <c r="E25" s="6">
         <v>75.90000000000001</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="89">
   <si>
     <t>Дата</t>
   </si>
@@ -35,6 +35,9 @@
   </si>
   <si>
     <t>Тип количество</t>
+  </si>
+  <si>
+    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -677,7 +680,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N26"/>
+  <dimension ref="A1:O26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -690,13 +693,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.7109375" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" customWidth="1"/>
-    <col min="14" max="14" width="23.7109375" customWidth="1"/>
+    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
+    <col min="13" max="13" width="10.7109375" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" customWidth="1"/>
+    <col min="15" max="15" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:15">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -739,714 +742,765 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" spans="1:14">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F2">
-        <v>46.1</v>
+        <v>46.104</v>
       </c>
       <c r="G2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H2">
+        <v>1.399</v>
+      </c>
+      <c r="I2" s="1">
         <v>1.6</v>
       </c>
-      <c r="I2" s="1">
-        <v>73.76000000000001</v>
-      </c>
       <c r="J2">
+        <v>73.7664</v>
+      </c>
+      <c r="K2" s="1">
         <v>1.63</v>
       </c>
-      <c r="K2" s="1">
-        <v>75.14</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1">
+        <v>75.14952</v>
+      </c>
+      <c r="M2" t="s">
+        <v>51</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3">
+        <v>26.182</v>
+      </c>
+      <c r="G3" t="s">
         <v>50</v>
       </c>
-      <c r="M2">
+      <c r="H3">
+        <v>1.401</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J3">
+        <v>39.53482</v>
+      </c>
+      <c r="K3" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L3" s="1">
+        <v>40.32028</v>
+      </c>
+      <c r="M3" t="s">
+        <v>52</v>
+      </c>
+      <c r="N3">
         <v>0</v>
       </c>
-      <c r="N2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
-      <c r="A3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>36</v>
-      </c>
-      <c r="E3" t="s">
-        <v>46</v>
-      </c>
-      <c r="F3">
-        <v>26.18</v>
-      </c>
-      <c r="G3" t="s">
-        <v>49</v>
-      </c>
-      <c r="H3">
-        <v>1.51</v>
-      </c>
-      <c r="I3" s="1">
-        <v>39.53</v>
-      </c>
-      <c r="J3">
-        <v>1.54</v>
-      </c>
-      <c r="K3" s="1">
-        <v>40.32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>51</v>
-      </c>
-      <c r="M3">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+      <c r="O3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F4">
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H4">
+        <v>1.619</v>
+      </c>
+      <c r="I4" s="1">
         <v>1.93</v>
       </c>
-      <c r="I4" s="1">
+      <c r="J4">
         <v>121.59</v>
       </c>
-      <c r="J4">
+      <c r="K4" s="1">
         <v>1.96</v>
       </c>
-      <c r="K4" s="1">
+      <c r="L4" s="1">
         <v>123.48</v>
       </c>
-      <c r="L4" t="s">
-        <v>52</v>
-      </c>
-      <c r="M4">
+      <c r="M4" t="s">
+        <v>53</v>
+      </c>
+      <c r="N4">
         <v>0</v>
       </c>
-      <c r="N4" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+      <c r="O4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s">
+        <v>39</v>
+      </c>
+      <c r="E5" t="s">
+        <v>47</v>
+      </c>
+      <c r="F5">
+        <v>26.766</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5">
+        <v>1.401</v>
+      </c>
+      <c r="I5" s="1">
+        <v>1.51</v>
+      </c>
+      <c r="J5">
+        <v>40.41666</v>
+      </c>
+      <c r="K5" s="1">
+        <v>1.54</v>
+      </c>
+      <c r="L5" s="1">
+        <v>41.21964</v>
+      </c>
+      <c r="M5" t="s">
+        <v>54</v>
+      </c>
+      <c r="N5">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
         <v>28</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" t="s">
         <v>38</v>
       </c>
-      <c r="E5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F5">
-        <v>26.77</v>
-      </c>
-      <c r="G5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5">
-        <v>1.51</v>
-      </c>
-      <c r="I5" s="1">
-        <v>40.42</v>
-      </c>
-      <c r="J5">
-        <v>1.54</v>
-      </c>
-      <c r="K5" s="1">
-        <v>41.23</v>
-      </c>
-      <c r="L5" t="s">
-        <v>53</v>
-      </c>
-      <c r="M5">
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6">
+        <v>40.399</v>
+      </c>
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>1.619</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1.95</v>
+      </c>
+      <c r="J6">
+        <v>78.77804999999999</v>
+      </c>
+      <c r="K6" s="1">
+        <v>1.98</v>
+      </c>
+      <c r="L6" s="1">
+        <v>79.99002</v>
+      </c>
+      <c r="M6" t="s">
+        <v>55</v>
+      </c>
+      <c r="N6">
         <v>0</v>
       </c>
-      <c r="N5" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
-      <c r="A6" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="O6" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" t="s">
         <v>27</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D7" t="s">
         <v>37</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E7" t="s">
         <v>47</v>
-      </c>
-      <c r="F6">
-        <v>40.4</v>
-      </c>
-      <c r="G6" t="s">
-        <v>49</v>
-      </c>
-      <c r="H6">
-        <v>1.95</v>
-      </c>
-      <c r="I6" s="1">
-        <v>78.78</v>
-      </c>
-      <c r="J6">
-        <v>1.98</v>
-      </c>
-      <c r="K6" s="1">
-        <v>79.98999999999999</v>
-      </c>
-      <c r="L6" t="s">
-        <v>54</v>
-      </c>
-      <c r="M6">
-        <v>0</v>
-      </c>
-      <c r="N6" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" t="s">
-        <v>23</v>
-      </c>
-      <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>36</v>
-      </c>
-      <c r="E7" t="s">
-        <v>46</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H7">
+        <v>1.401</v>
+      </c>
+      <c r="I7" s="1">
         <v>1.51</v>
       </c>
-      <c r="I7" s="1">
+      <c r="J7">
         <v>42.28</v>
       </c>
-      <c r="J7">
+      <c r="K7" s="1">
         <v>1.54</v>
       </c>
-      <c r="K7" s="1">
+      <c r="L7" s="1">
         <v>43.12</v>
       </c>
-      <c r="L7" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7">
+      <c r="M7" t="s">
+        <v>56</v>
+      </c>
+      <c r="N7">
         <v>0</v>
       </c>
-      <c r="N7" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+      <c r="O7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D8" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E8" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F8">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H8">
+        <v>1.401</v>
+      </c>
+      <c r="I8" s="1">
         <v>1.51</v>
       </c>
-      <c r="I8" s="1">
+      <c r="J8">
         <v>45.3</v>
       </c>
-      <c r="J8">
+      <c r="K8" s="1">
         <v>1.54</v>
       </c>
-      <c r="K8" s="1">
+      <c r="L8" s="1">
         <v>46.2</v>
       </c>
-      <c r="L8" t="s">
-        <v>56</v>
-      </c>
-      <c r="M8">
+      <c r="M8" t="s">
+        <v>57</v>
+      </c>
+      <c r="N8">
         <v>0</v>
       </c>
-      <c r="N8" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+      <c r="O8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
       <c r="A9" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F9">
         <v>19.5</v>
       </c>
       <c r="G9" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H9">
+        <v>1.401</v>
+      </c>
+      <c r="I9" s="1">
         <v>1.51</v>
       </c>
-      <c r="I9" s="1">
-        <v>29.44</v>
-      </c>
       <c r="J9">
+        <v>29.445</v>
+      </c>
+      <c r="K9" s="1">
         <v>1.54</v>
       </c>
-      <c r="K9" s="1">
+      <c r="L9" s="1">
         <v>30.03</v>
       </c>
-      <c r="L9" t="s">
-        <v>57</v>
-      </c>
-      <c r="M9">
+      <c r="M9" t="s">
+        <v>58</v>
+      </c>
+      <c r="N9">
         <v>0</v>
       </c>
-      <c r="N9" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+      <c r="O9" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E10" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10">
         <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H10">
+        <v>1.619</v>
+      </c>
+      <c r="I10" s="1">
         <v>1.95</v>
       </c>
-      <c r="I10" s="1">
+      <c r="J10">
         <v>97.5</v>
       </c>
-      <c r="J10">
+      <c r="K10" s="1">
         <v>1.98</v>
       </c>
-      <c r="K10" s="1">
+      <c r="L10" s="1">
         <v>99</v>
       </c>
-      <c r="L10" t="s">
-        <v>58</v>
-      </c>
-      <c r="M10">
+      <c r="M10" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10">
         <v>0</v>
       </c>
-      <c r="N10" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+      <c r="O10" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="A11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E11" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F11">
         <v>43</v>
       </c>
       <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="H11">
+        <v>1.401</v>
+      </c>
+      <c r="I11" s="1">
+        <v>1.53</v>
+      </c>
+      <c r="J11">
+        <v>65.79000000000001</v>
+      </c>
+      <c r="K11" s="1">
+        <v>1.56</v>
+      </c>
+      <c r="L11" s="1">
+        <v>67.08</v>
+      </c>
+      <c r="M11" t="s">
+        <v>60</v>
+      </c>
+      <c r="N11">
+        <v>0</v>
+      </c>
+      <c r="O11" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B12" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12">
+        <v>19.006</v>
+      </c>
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12">
+        <v>1.441</v>
+      </c>
+      <c r="I12" s="1">
+        <v>1.52</v>
+      </c>
+      <c r="J12">
+        <v>28.88912</v>
+      </c>
+      <c r="K12" s="1">
+        <v>1.55</v>
+      </c>
+      <c r="L12" s="1">
+        <v>29.4593</v>
+      </c>
+      <c r="M12" t="s">
+        <v>61</v>
+      </c>
+      <c r="N12">
+        <v>0</v>
+      </c>
+      <c r="O12" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>20</v>
+      </c>
+      <c r="B13" t="s">
+        <v>22</v>
+      </c>
+      <c r="C13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D13" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" t="s">
         <v>49</v>
       </c>
-      <c r="H11">
-        <v>1.53</v>
-      </c>
-      <c r="I11" s="1">
-        <v>65.79000000000001</v>
-      </c>
-      <c r="J11">
-        <v>1.56</v>
-      </c>
-      <c r="K11" s="1">
-        <v>67.08</v>
-      </c>
-      <c r="L11" t="s">
-        <v>59</v>
-      </c>
-      <c r="M11">
-        <v>0</v>
-      </c>
-      <c r="N11" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>41</v>
-      </c>
-      <c r="E12" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12">
-        <v>19.01</v>
-      </c>
-      <c r="G12" t="s">
-        <v>49</v>
-      </c>
-      <c r="H12">
-        <v>1.52</v>
-      </c>
-      <c r="I12" s="1">
-        <v>28.9</v>
-      </c>
-      <c r="J12">
-        <v>1.55</v>
-      </c>
-      <c r="K12" s="1">
-        <v>29.47</v>
-      </c>
-      <c r="L12" t="s">
-        <v>60</v>
-      </c>
-      <c r="M12">
-        <v>0</v>
-      </c>
-      <c r="N12" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" t="s">
-        <v>39</v>
-      </c>
-      <c r="E13" t="s">
-        <v>48</v>
-      </c>
       <c r="F13">
-        <v>19.06</v>
+        <v>19.055</v>
       </c>
       <c r="G13" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H13">
         <v>1.81</v>
       </c>
       <c r="I13" s="1">
-        <v>34.5</v>
+        <v>1.81</v>
       </c>
       <c r="J13">
+        <v>34.48955</v>
+      </c>
+      <c r="K13" s="1">
         <v>1.81</v>
       </c>
-      <c r="K13" s="1">
-        <v>34.5</v>
-      </c>
-      <c r="L13" t="s">
-        <v>61</v>
-      </c>
-      <c r="M13">
+      <c r="L13" s="1">
+        <v>34.48955</v>
+      </c>
+      <c r="M13" t="s">
+        <v>62</v>
+      </c>
+      <c r="N13">
         <v>0</v>
       </c>
-      <c r="N13" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+      <c r="O13" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F14">
         <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H14">
         <v>1.8</v>
       </c>
       <c r="I14" s="1">
+        <v>1.8</v>
+      </c>
+      <c r="J14">
         <v>41.4</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>1.8</v>
       </c>
-      <c r="K14" s="1">
+      <c r="L14" s="1">
         <v>41.4</v>
       </c>
-      <c r="L14" t="s">
-        <v>62</v>
-      </c>
-      <c r="M14">
+      <c r="M14" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14">
         <v>0</v>
       </c>
-      <c r="N14" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+      <c r="O14" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="A15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B15" t="s">
+        <v>22</v>
+      </c>
+      <c r="C15" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" t="s">
+        <v>43</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15">
+        <v>24.748</v>
+      </c>
+      <c r="G15" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15">
+        <v>1.619</v>
+      </c>
+      <c r="I15" s="1">
+        <v>1.99</v>
+      </c>
+      <c r="J15">
+        <v>49.24852</v>
+      </c>
+      <c r="K15" s="1">
+        <v>2.02</v>
+      </c>
+      <c r="L15" s="1">
+        <v>49.99096</v>
+      </c>
+      <c r="M15" t="s">
+        <v>64</v>
+      </c>
+      <c r="N15">
+        <v>0</v>
+      </c>
+      <c r="O15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
         <v>21</v>
       </c>
-      <c r="C15" t="s">
-        <v>32</v>
-      </c>
-      <c r="D15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s">
-        <v>47</v>
-      </c>
-      <c r="F15">
-        <v>24.75</v>
-      </c>
-      <c r="G15" t="s">
-        <v>49</v>
-      </c>
-      <c r="H15">
-        <v>1.99</v>
-      </c>
-      <c r="I15" s="1">
-        <v>49.25</v>
-      </c>
-      <c r="J15">
-        <v>2.02</v>
-      </c>
-      <c r="K15" s="1">
-        <v>50</v>
-      </c>
-      <c r="L15" t="s">
-        <v>63</v>
-      </c>
-      <c r="M15">
-        <v>0</v>
-      </c>
-      <c r="N15" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" t="s">
-        <v>20</v>
-      </c>
       <c r="B16" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F16">
         <v>48.52</v>
       </c>
       <c r="G16" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H16">
+        <v>1.619</v>
+      </c>
+      <c r="I16" s="1">
         <v>1.99</v>
       </c>
-      <c r="I16" s="1">
-        <v>96.55</v>
-      </c>
       <c r="J16">
+        <v>96.5548</v>
+      </c>
+      <c r="K16" s="1">
         <v>2.02</v>
       </c>
-      <c r="K16" s="1">
-        <v>98.01000000000001</v>
-      </c>
-      <c r="L16" t="s">
-        <v>64</v>
-      </c>
-      <c r="M16">
+      <c r="L16" s="1">
+        <v>98.0104</v>
+      </c>
+      <c r="M16" t="s">
+        <v>65</v>
+      </c>
+      <c r="N16">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+      <c r="O16" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B17" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D17" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E17" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F17">
         <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H17">
+        <v>1.619</v>
+      </c>
+      <c r="I17" s="1">
         <v>1.99</v>
       </c>
-      <c r="I17" s="1">
+      <c r="J17">
         <v>109.45</v>
       </c>
-      <c r="J17">
+      <c r="K17" s="1">
         <v>2.02</v>
       </c>
-      <c r="K17" s="1">
+      <c r="L17" s="1">
         <v>111.1</v>
       </c>
-      <c r="L17" t="s">
-        <v>65</v>
-      </c>
-      <c r="M17">
+      <c r="M17" t="s">
+        <v>66</v>
+      </c>
+      <c r="N17">
         <v>0</v>
       </c>
-      <c r="N17" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+      <c r="O17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15">
       <c r="A20" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1454,72 +1508,72 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:15">
       <c r="A21" s="4" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15">
       <c r="A22" s="5" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B22" s="6">
-        <v>281.67</v>
+        <v>281.667</v>
       </c>
       <c r="C22" s="6">
         <v>6</v>
       </c>
       <c r="D22" s="7">
-        <v>1.963716</v>
+        <v>1.963742</v>
       </c>
       <c r="E22" s="6">
         <v>553.12</v>
       </c>
       <c r="F22" s="6">
-        <v>561.58</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+        <v>561.5700000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="A23" s="5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B23" s="6">
-        <v>192.46</v>
+        <v>192.454</v>
       </c>
       <c r="C23" s="6">
         <v>7</v>
       </c>
       <c r="D23" s="7">
-        <v>1.515432</v>
+        <v>1.515456</v>
       </c>
       <c r="E23" s="6">
         <v>291.66</v>
       </c>
       <c r="F23" s="6">
-        <v>297.45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+        <v>297.43</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15">
       <c r="A24" s="5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B24" s="6">
-        <v>46.1</v>
+        <v>46.104</v>
       </c>
       <c r="C24" s="6">
         <v>1</v>
@@ -1528,38 +1582,38 @@
         <v>1.6</v>
       </c>
       <c r="E24" s="6">
-        <v>73.76000000000001</v>
+        <v>73.77</v>
       </c>
       <c r="F24" s="6">
-        <v>75.14</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+        <v>75.15000000000001</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15">
       <c r="A25" s="5" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B25" s="6">
-        <v>42.06</v>
+        <v>42.055</v>
       </c>
       <c r="C25" s="6">
         <v>2</v>
       </c>
       <c r="D25" s="7">
-        <v>1.804565</v>
+        <v>1.804531</v>
       </c>
       <c r="E25" s="6">
-        <v>75.90000000000001</v>
+        <v>75.89</v>
       </c>
       <c r="F25" s="6">
-        <v>75.90000000000001</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+        <v>75.89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15">
       <c r="A26" s="8" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B26" s="9">
-        <v>562.29</v>
+        <v>562.28</v>
       </c>
       <c r="C26" s="9">
         <v>16</v>
@@ -1569,7 +1623,7 @@
         <v>994.4400000000001</v>
       </c>
       <c r="F26" s="9">
-        <v>1010.07</v>
+        <v>1010.04</v>
       </c>
     </row>
   </sheetData>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="88">
   <si>
     <t>Дата</t>
   </si>
@@ -35,9 +35,6 @@
   </si>
   <si>
     <t>Тип количество</t>
-  </si>
-  <si>
-    <t>Базова ЕКО цена</t>
   </si>
   <si>
     <t>GTA цена</t>
@@ -288,8 +285,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="#,##0.00"/>
-    <numFmt numFmtId="165" formatCode="#,##0.000000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -382,10 +379,10 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -680,7 +677,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O26"/>
+  <dimension ref="A1:N26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="35.7109375" customWidth="1"/>
@@ -693,13 +690,13 @@
     <col min="8" max="8" width="23.7109375" customWidth="1"/>
     <col min="9" max="9" width="15.7109375" style="1" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="12" width="15.7109375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="10.7109375" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" customWidth="1"/>
-    <col min="15" max="15" width="23.7109375" customWidth="1"/>
+    <col min="11" max="11" width="15.7109375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.7109375" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" customWidth="1"/>
+    <col min="14" max="14" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -742,765 +739,714 @@
       <c r="N1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="O1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="2" spans="1:15">
-      <c r="A2" t="s">
-        <v>15</v>
-      </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2">
         <v>46.104</v>
       </c>
       <c r="G2" t="s">
+        <v>49</v>
+      </c>
+      <c r="H2">
+        <v>1.6</v>
+      </c>
+      <c r="I2" s="1">
+        <v>73.76600000000001</v>
+      </c>
+      <c r="J2">
+        <v>1.63</v>
+      </c>
+      <c r="K2" s="1">
+        <v>75.15000000000001</v>
+      </c>
+      <c r="L2" t="s">
         <v>50</v>
       </c>
-      <c r="H2">
-        <v>1.399</v>
-      </c>
-      <c r="I2" s="1">
-        <v>1.6</v>
-      </c>
-      <c r="J2">
-        <v>73.7664</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1.63</v>
-      </c>
-      <c r="L2" s="1">
-        <v>75.14952</v>
-      </c>
-      <c r="M2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
-      <c r="O2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:15">
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3">
         <v>26.182</v>
       </c>
       <c r="G3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H3">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I3" s="1">
-        <v>1.51</v>
+        <v>39.535</v>
       </c>
       <c r="J3">
-        <v>39.53482</v>
+        <v>1.54</v>
       </c>
       <c r="K3" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L3" s="1">
-        <v>40.32028</v>
-      </c>
-      <c r="M3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
-      <c r="O3" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:15">
+        <v>40.32</v>
+      </c>
+      <c r="L3" t="s">
+        <v>51</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F4">
         <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H4">
-        <v>1.619</v>
+        <v>1.93</v>
       </c>
       <c r="I4" s="1">
-        <v>1.93</v>
+        <v>121.59</v>
       </c>
       <c r="J4">
-        <v>121.59</v>
+        <v>1.96</v>
       </c>
       <c r="K4" s="1">
-        <v>1.96</v>
-      </c>
-      <c r="L4" s="1">
         <v>123.48</v>
       </c>
-      <c r="M4" t="s">
-        <v>53</v>
-      </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
-      <c r="O4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="5" spans="1:15">
+      <c r="L4" t="s">
+        <v>52</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F5">
         <v>26.766</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H5">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I5" s="1">
-        <v>1.51</v>
+        <v>40.417</v>
       </c>
       <c r="J5">
-        <v>40.41666</v>
+        <v>1.54</v>
       </c>
       <c r="K5" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L5" s="1">
-        <v>41.21964</v>
-      </c>
-      <c r="M5" t="s">
-        <v>54</v>
-      </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
-      <c r="O5" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="1:15">
+        <v>41.22</v>
+      </c>
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5">
+        <v>0</v>
+      </c>
+      <c r="N5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F6">
         <v>40.399</v>
       </c>
       <c r="G6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H6">
-        <v>1.619</v>
+        <v>1.95</v>
       </c>
       <c r="I6" s="1">
-        <v>1.95</v>
+        <v>78.77800000000001</v>
       </c>
       <c r="J6">
-        <v>78.77804999999999</v>
+        <v>1.98</v>
       </c>
       <c r="K6" s="1">
-        <v>1.98</v>
-      </c>
-      <c r="L6" s="1">
-        <v>79.99002</v>
-      </c>
-      <c r="M6" t="s">
-        <v>55</v>
-      </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:15">
+        <v>79.98999999999999</v>
+      </c>
+      <c r="L6" t="s">
+        <v>54</v>
+      </c>
+      <c r="M6">
+        <v>0</v>
+      </c>
+      <c r="N6" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7">
         <v>28</v>
       </c>
       <c r="G7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H7">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I7" s="1">
-        <v>1.51</v>
+        <v>42.28</v>
       </c>
       <c r="J7">
-        <v>42.28</v>
+        <v>1.54</v>
       </c>
       <c r="K7" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L7" s="1">
         <v>43.12</v>
       </c>
-      <c r="M7" t="s">
-        <v>56</v>
-      </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
-      <c r="O7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="8" spans="1:15">
+      <c r="L7" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7">
+        <v>0</v>
+      </c>
+      <c r="N7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F8">
         <v>30</v>
       </c>
       <c r="G8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H8">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I8" s="1">
-        <v>1.51</v>
+        <v>45.3</v>
       </c>
       <c r="J8">
-        <v>45.3</v>
+        <v>1.54</v>
       </c>
       <c r="K8" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L8" s="1">
         <v>46.2</v>
       </c>
-      <c r="M8" t="s">
-        <v>57</v>
-      </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
-      <c r="O8" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="9" spans="1:15">
+      <c r="L8" t="s">
+        <v>56</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E9" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>19.5</v>
       </c>
       <c r="G9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H9">
-        <v>1.401</v>
+        <v>1.51</v>
       </c>
       <c r="I9" s="1">
-        <v>1.51</v>
+        <v>29.445</v>
       </c>
       <c r="J9">
-        <v>29.445</v>
+        <v>1.54</v>
       </c>
       <c r="K9" s="1">
-        <v>1.54</v>
-      </c>
-      <c r="L9" s="1">
         <v>30.03</v>
       </c>
-      <c r="M9" t="s">
-        <v>58</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="10" spans="1:15">
+      <c r="L9" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D10" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>50</v>
       </c>
       <c r="G10" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H10">
-        <v>1.619</v>
+        <v>1.95</v>
       </c>
       <c r="I10" s="1">
-        <v>1.95</v>
+        <v>97.5</v>
       </c>
       <c r="J10">
-        <v>97.5</v>
+        <v>1.98</v>
       </c>
       <c r="K10" s="1">
-        <v>1.98</v>
-      </c>
-      <c r="L10" s="1">
         <v>99</v>
       </c>
-      <c r="M10" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
-      <c r="O10" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="11" spans="1:15">
+      <c r="L10" t="s">
+        <v>58</v>
+      </c>
+      <c r="M10">
+        <v>0</v>
+      </c>
+      <c r="N10" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F11">
         <v>43</v>
       </c>
       <c r="G11" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H11">
-        <v>1.401</v>
+        <v>1.53</v>
       </c>
       <c r="I11" s="1">
-        <v>1.53</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="J11">
-        <v>65.79000000000001</v>
+        <v>1.56</v>
       </c>
       <c r="K11" s="1">
-        <v>1.56</v>
-      </c>
-      <c r="L11" s="1">
         <v>67.08</v>
       </c>
-      <c r="M11" t="s">
-        <v>60</v>
-      </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
-      <c r="O11" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="12" spans="1:15">
+      <c r="L11" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11">
+        <v>0</v>
+      </c>
+      <c r="N11" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F12">
         <v>19.006</v>
       </c>
       <c r="G12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H12">
-        <v>1.441</v>
+        <v>1.52</v>
       </c>
       <c r="I12" s="1">
-        <v>1.52</v>
+        <v>28.889</v>
       </c>
       <c r="J12">
-        <v>28.88912</v>
+        <v>1.55</v>
       </c>
       <c r="K12" s="1">
-        <v>1.55</v>
-      </c>
-      <c r="L12" s="1">
-        <v>29.4593</v>
-      </c>
-      <c r="M12" t="s">
-        <v>61</v>
-      </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
-      <c r="O12" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:15">
+        <v>29.459</v>
+      </c>
+      <c r="L12" t="s">
+        <v>60</v>
+      </c>
+      <c r="M12">
+        <v>0</v>
+      </c>
+      <c r="N12" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F13">
         <v>19.055</v>
       </c>
       <c r="G13" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H13">
         <v>1.81</v>
       </c>
       <c r="I13" s="1">
+        <v>34.49</v>
+      </c>
+      <c r="J13">
         <v>1.81</v>
       </c>
-      <c r="J13">
-        <v>34.48955</v>
-      </c>
       <c r="K13" s="1">
-        <v>1.81</v>
-      </c>
-      <c r="L13" s="1">
-        <v>34.48955</v>
-      </c>
-      <c r="M13" t="s">
-        <v>62</v>
-      </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
-      <c r="O13" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="14" spans="1:15">
+        <v>34.49</v>
+      </c>
+      <c r="L13" t="s">
+        <v>61</v>
+      </c>
+      <c r="M13">
+        <v>0</v>
+      </c>
+      <c r="N13" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
-        <v>22</v>
-      </c>
       <c r="C14" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="F14">
         <v>23</v>
       </c>
       <c r="G14" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H14">
         <v>1.8</v>
       </c>
       <c r="I14" s="1">
+        <v>41.4</v>
+      </c>
+      <c r="J14">
         <v>1.8</v>
       </c>
-      <c r="J14">
+      <c r="K14" s="1">
         <v>41.4</v>
       </c>
-      <c r="K14" s="1">
-        <v>1.8</v>
-      </c>
-      <c r="L14" s="1">
-        <v>41.4</v>
-      </c>
-      <c r="M14" t="s">
-        <v>63</v>
-      </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
-      <c r="O14" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="15" spans="1:15">
+      <c r="L14" t="s">
+        <v>62</v>
+      </c>
+      <c r="M14">
+        <v>0</v>
+      </c>
+      <c r="N14" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="B15" t="s">
         <v>21</v>
       </c>
-      <c r="B15" t="s">
-        <v>22</v>
-      </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15">
         <v>24.748</v>
       </c>
       <c r="G15" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H15">
-        <v>1.619</v>
+        <v>1.99</v>
       </c>
       <c r="I15" s="1">
-        <v>1.99</v>
+        <v>49.249</v>
       </c>
       <c r="J15">
-        <v>49.24852</v>
+        <v>2.02</v>
       </c>
       <c r="K15" s="1">
-        <v>2.02</v>
-      </c>
-      <c r="L15" s="1">
-        <v>49.99096</v>
-      </c>
-      <c r="M15" t="s">
-        <v>64</v>
-      </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
-      <c r="O15" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="16" spans="1:15">
+        <v>49.991</v>
+      </c>
+      <c r="L15" t="s">
+        <v>63</v>
+      </c>
+      <c r="M15">
+        <v>0</v>
+      </c>
+      <c r="N15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" t="s">
         <v>21</v>
       </c>
-      <c r="B16" t="s">
-        <v>22</v>
-      </c>
       <c r="C16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F16">
         <v>48.52</v>
       </c>
       <c r="G16" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H16">
-        <v>1.619</v>
+        <v>1.99</v>
       </c>
       <c r="I16" s="1">
-        <v>1.99</v>
+        <v>96.55500000000001</v>
       </c>
       <c r="J16">
-        <v>96.5548</v>
+        <v>2.02</v>
       </c>
       <c r="K16" s="1">
-        <v>2.02</v>
-      </c>
-      <c r="L16" s="1">
-        <v>98.0104</v>
-      </c>
-      <c r="M16" t="s">
-        <v>65</v>
-      </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
-      <c r="O16" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15">
+        <v>98.01000000000001</v>
+      </c>
+      <c r="L16" t="s">
+        <v>64</v>
+      </c>
+      <c r="M16">
+        <v>0</v>
+      </c>
+      <c r="N16" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D17" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F17">
         <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="H17">
-        <v>1.619</v>
+        <v>1.99</v>
       </c>
       <c r="I17" s="1">
-        <v>1.99</v>
+        <v>109.45</v>
       </c>
       <c r="J17">
-        <v>109.45</v>
+        <v>2.02</v>
       </c>
       <c r="K17" s="1">
-        <v>2.02</v>
-      </c>
-      <c r="L17" s="1">
         <v>111.1</v>
       </c>
-      <c r="M17" t="s">
-        <v>66</v>
-      </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
-      <c r="O17" t="s">
+      <c r="L17" t="s">
+        <v>65</v>
+      </c>
+      <c r="M17">
+        <v>0</v>
+      </c>
+      <c r="N17" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
+      <c r="A20" s="3" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15">
-      <c r="A20" s="3" t="s">
-        <v>83</v>
       </c>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1508,109 +1454,109 @@
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
     </row>
-    <row r="21" spans="1:15">
+    <row r="21" spans="1:14">
       <c r="A21" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>87</v>
-      </c>
       <c r="E21" s="4" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="22" spans="1:15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" s="5" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B22" s="6">
         <v>281.667</v>
       </c>
-      <c r="C22" s="6">
+      <c r="C22" s="7">
         <v>6</v>
       </c>
       <c r="D22" s="7">
-        <v>1.963742</v>
-      </c>
-      <c r="E22" s="6">
-        <v>553.12</v>
-      </c>
-      <c r="F22" s="6">
-        <v>561.5700000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15">
+        <v>1.964</v>
+      </c>
+      <c r="E22" s="7">
+        <v>553.122</v>
+      </c>
+      <c r="F22" s="7">
+        <v>561.571</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B23" s="6">
         <v>192.454</v>
       </c>
-      <c r="C23" s="6">
+      <c r="C23" s="7">
         <v>7</v>
       </c>
       <c r="D23" s="7">
-        <v>1.515456</v>
-      </c>
-      <c r="E23" s="6">
-        <v>291.66</v>
-      </c>
-      <c r="F23" s="6">
-        <v>297.43</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15">
+        <v>1.515</v>
+      </c>
+      <c r="E23" s="7">
+        <v>291.656</v>
+      </c>
+      <c r="F23" s="7">
+        <v>297.429</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" s="5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" s="6">
         <v>46.104</v>
       </c>
-      <c r="C24" s="6">
+      <c r="C24" s="7">
         <v>1</v>
       </c>
       <c r="D24" s="7">
         <v>1.6</v>
       </c>
-      <c r="E24" s="6">
-        <v>73.77</v>
-      </c>
-      <c r="F24" s="6">
+      <c r="E24" s="7">
+        <v>73.76600000000001</v>
+      </c>
+      <c r="F24" s="7">
         <v>75.15000000000001</v>
       </c>
     </row>
-    <row r="25" spans="1:15">
+    <row r="25" spans="1:14">
       <c r="A25" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B25" s="6">
         <v>42.055</v>
       </c>
-      <c r="C25" s="6">
+      <c r="C25" s="7">
         <v>2</v>
       </c>
       <c r="D25" s="7">
-        <v>1.804531</v>
-      </c>
-      <c r="E25" s="6">
+        <v>1.805</v>
+      </c>
+      <c r="E25" s="7">
         <v>75.89</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="7">
         <v>75.89</v>
       </c>
     </row>
-    <row r="26" spans="1:15">
+    <row r="26" spans="1:14">
       <c r="A26" s="8" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B26" s="9">
         <v>562.28</v>
@@ -1620,7 +1566,7 @@
       </c>
       <c r="D26" s="7"/>
       <c r="E26" s="9">
-        <v>994.4400000000001</v>
+        <v>994.434</v>
       </c>
       <c r="F26" s="9">
         <v>1010.04</v>

--- a/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ.xlsx
+++ b/SPLIT_COMPANY_DATA/RESULT/companies_result/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ/ТРАКИЙСКИ УНИВЕРСИТЕТ % 3 - РЕКТОРАТ.xlsx
@@ -883,10 +883,10 @@
         <v>66</v>
       </c>
       <c r="H2" s="1">
-        <v>1.669</v>
+        <v>1.75</v>
       </c>
       <c r="I2" s="1">
-        <v>76.774</v>
+        <v>80.5</v>
       </c>
       <c r="J2" s="1">
         <v>1.78</v>
@@ -927,10 +927,10 @@
         <v>66</v>
       </c>
       <c r="H3" s="1">
-        <v>1.429</v>
+        <v>1.51</v>
       </c>
       <c r="I3" s="1">
-        <v>17.148</v>
+        <v>18.12</v>
       </c>
       <c r="J3" s="1">
         <v>1.54</v>
@@ -971,10 +971,10 @@
         <v>66</v>
       </c>
       <c r="H4" s="1">
-        <v>1.677</v>
+        <v>1.76</v>
       </c>
       <c r="I4" s="1">
-        <v>18.732</v>
+        <v>19.659</v>
       </c>
       <c r="J4" s="1">
         <v>1.79</v>
@@ -1015,10 +1015,10 @@
         <v>66</v>
       </c>
       <c r="H5" s="1">
-        <v>1.677</v>
+        <v>1.76</v>
       </c>
       <c r="I5" s="1">
-        <v>85.00700000000001</v>
+        <v>89.214</v>
       </c>
       <c r="J5" s="1">
         <v>1.79</v>
@@ -1059,10 +1059,10 @@
         <v>66</v>
       </c>
       <c r="H6" s="1">
-        <v>1.766</v>
+        <v>2.02</v>
       </c>
       <c r="I6" s="1">
-        <v>98.48999999999999</v>
+        <v>112.655</v>
       </c>
       <c r="J6" s="1">
         <v>2.05</v>
@@ -1103,10 +1103,10 @@
         <v>66</v>
       </c>
       <c r="H7" s="1">
-        <v>1.663</v>
+        <v>1.76</v>
       </c>
       <c r="I7" s="1">
-        <v>68.848</v>
+        <v>72.864</v>
       </c>
       <c r="J7" s="1">
         <v>1.79</v>
@@ -1147,10 +1147,10 @@
         <v>66</v>
       </c>
       <c r="H8" s="1">
-        <v>1.779</v>
+        <v>2.02</v>
       </c>
       <c r="I8" s="1">
-        <v>73.77500000000001</v>
+        <v>83.76900000000001</v>
       </c>
       <c r="J8" s="1">
         <v>2.05</v>
@@ -1191,10 +1191,10 @@
         <v>66</v>
       </c>
       <c r="H9" s="1">
-        <v>1.644</v>
+        <v>1.77</v>
       </c>
       <c r="I9" s="1">
-        <v>61.979</v>
+        <v>66.729</v>
       </c>
       <c r="J9" s="1">
         <v>1.8</v>
@@ -1235,10 +1235,10 @@
         <v>66</v>
       </c>
       <c r="H10" s="1">
-        <v>1.769</v>
+        <v>2.01</v>
       </c>
       <c r="I10" s="1">
-        <v>81.374</v>
+        <v>92.45999999999999</v>
       </c>
       <c r="J10" s="1">
         <v>2.04</v>
@@ -1279,10 +1279,10 @@
         <v>66</v>
       </c>
       <c r="H11" s="1">
-        <v>1.769</v>
+        <v>2.02</v>
       </c>
       <c r="I11" s="1">
-        <v>104.601</v>
+        <v>119.443</v>
       </c>
       <c r="J11" s="1">
         <v>2.05</v>
@@ -1323,10 +1323,10 @@
         <v>66</v>
       </c>
       <c r="H12" s="1">
-        <v>1.769</v>
+        <v>2.02</v>
       </c>
       <c r="I12" s="1">
-        <v>78.738</v>
+        <v>89.91</v>
       </c>
       <c r="J12" s="1">
         <v>2.05</v>
@@ -1367,10 +1367,10 @@
         <v>66</v>
       </c>
       <c r="H13" s="1">
-        <v>1.769</v>
+        <v>2.02</v>
       </c>
       <c r="I13" s="1">
-        <v>60.712</v>
+        <v>69.32599999999999</v>
       </c>
       <c r="J13" s="1">
         <v>2.05</v>
@@ -1411,10 +1411,10 @@
         <v>66</v>
       </c>
       <c r="H14" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I14" s="1">
-        <v>48.3</v>
+        <v>51.376</v>
       </c>
       <c r="J14" s="1">
         <v>1.55</v>
@@ -1455,10 +1455,10 @@
         <v>66</v>
       </c>
       <c r="H15" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I15" s="1">
-        <v>48.586</v>
+        <v>51.68</v>
       </c>
       <c r="J15" s="1">
         <v>1.55</v>
@@ -1499,10 +1499,10 @@
         <v>66</v>
       </c>
       <c r="H16" s="1">
-        <v>1.677</v>
+        <v>1.77</v>
       </c>
       <c r="I16" s="1">
-        <v>122.505</v>
+        <v>129.298</v>
       </c>
       <c r="J16" s="1">
         <v>1.8</v>
@@ -1543,10 +1543,10 @@
         <v>66</v>
       </c>
       <c r="H17" s="1">
-        <v>1.429</v>
+        <v>1.52</v>
       </c>
       <c r="I17" s="1">
-        <v>57.16</v>
+        <v>60.8</v>
       </c>
       <c r="J17" s="1">
         <v>1.55</v>
@@ -1587,10 +1587,10 @@
         <v>66</v>
       </c>
       <c r="H18" s="1">
-        <v>1.799</v>
+        <v>2.07</v>
       </c>
       <c r="I18" s="1">
-        <v>98.94499999999999</v>
+        <v>113.85</v>
       </c>
       <c r="J18" s="1">
         <v>2.1</v>
@@ -1631,10 +1631,10 @@
         <v>66</v>
       </c>
       <c r="H19" s="1">
-        <v>1.799</v>
+        <v>2.07</v>
       </c>
       <c r="I19" s="1">
-        <v>107.94</v>
+        <v>124.2</v>
       </c>
       <c r="J19" s="1">
         <v>2.1</v>
@@ -1675,10 +1675,10 @@
         <v>66</v>
       </c>
       <c r="H20" s="1">
-        <v>1.799</v>
+        <v>2.07</v>
       </c>
       <c r="I20" s="1">
-        <v>76.547</v>
+        <v>88.078</v>
       </c>
       <c r="J20" s="1">
         <v>2.1</v>
@@ -1719,10 +1719,10 @@
         <v>66</v>
       </c>
       <c r="H21" s="1">
-        <v>1.429</v>
+        <v>1.54</v>
       </c>
       <c r="I21" s="1">
-        <v>50.015</v>
+        <v>53.9</v>
       </c>
       <c r="J21" s="1">
         <v>1.57</v>
@@ -1763,10 +1763,10 @@
         <v>66</v>
       </c>
       <c r="H22" s="1">
-        <v>1.708</v>
+        <v>1.82</v>
       </c>
       <c r="I22" s="1">
-        <v>108.987</v>
+        <v>116.134</v>
       </c>
       <c r="J22" s="1">
         <v>1.85</v>
@@ -1807,10 +1807,10 @@
         <v>66</v>
       </c>
       <c r="H23" s="1">
-        <v>1.459</v>
+        <v>1.55</v>
       </c>
       <c r="I23" s="1">
-        <v>55.457</v>
+        <v>58.916</v>
       </c>
       <c r="J23" s="1">
         <v>1.58</v>
@@ -1851,10 +1851,10 @@
         <v>66</v>
       </c>
       <c r="H24" s="1">
-        <v>1.719</v>
+        <v>1.82</v>
       </c>
       <c r="I24" s="1">
-        <v>82.839</v>
+        <v>87.706</v>
       </c>
       <c r="J24" s="1">
         <v>1.85</v>
@@ -1895,10 +1895,10 @@
         <v>66</v>
       </c>
       <c r="H25" s="1">
-        <v>1.819</v>
+        <v>2.08</v>
       </c>
       <c r="I25" s="1">
-        <v>81.855</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="J25" s="1">
         <v>2.11</v>
@@ -1939,10 +1939,10 @@
         <v>66</v>
       </c>
       <c r="H26" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I26" s="1">
-        <v>48.785</v>
+        <v>51.368</v>
       </c>
       <c r="J26" s="1">
         <v>1.84</v>
@@ -1983,10 +1983,10 @@
         <v>66</v>
       </c>
       <c r="H27" s="1">
-        <v>1.719</v>
+        <v>1.81</v>
       </c>
       <c r="I27" s="1">
-        <v>43.078</v>
+        <v>45.359</v>
       </c>
       <c r="J27" s="1">
         <v>1.84</v>
@@ -2027,10 +2027,10 @@
         <v>66</v>
       </c>
       <c r="H28" s="1">
-        <v>1.819</v>
+        <v>2.07</v>
       </c>
       <c r="I28" s="1">
-        <v>127.094</v>
+        <v>144.631</v>
       </c>
       <c r="J28" s="1">
         <v>2.1</v>
@@ -2089,10 +2089,10 @@
         <v>11</v>
       </c>
       <c r="D33" s="8">
-        <v>1.78836</v>
+        <v>2.04458</v>
       </c>
       <c r="E33" s="6">
-        <v>990.0700000000001</v>
+        <v>1131.92</v>
       </c>
       <c r="F33" s="6">
         <v>1148.53</v>
@@ -2109,10 +2109,10 @@
         <v>10</v>
       </c>
       <c r="D34" s="8">
-        <v>1.68653</v>
+        <v>1.7836</v>
       </c>
       <c r="E34" s="6">
-        <v>717.53</v>
+        <v>758.83</v>
       </c>
       <c r="F34" s="6">
         <v>771.59</v>
@@ -2129,10 +2129,10 @@
         <v>6</v>
       </c>
       <c r="D35" s="8">
-        <v>1.43492</v>
+        <v>1.52892</v>
       </c>
       <c r="E35" s="6">
-        <v>276.67</v>
+        <v>294.79</v>
       </c>
       <c r="F35" s="6">
         <v>300.58</v>
@@ -2150,7 +2150,7 @@
       </c>
       <c r="D36" s="8"/>
       <c r="E36" s="10">
-        <v>1984.27</v>
+        <v>2185.54</v>
       </c>
       <c r="F36" s="10">
         <v>2220.7</v>
